--- a/backend/data/financials_by_company/1782.HK.xlsx
+++ b/backend/data/financials_by_company/1782.HK.xlsx
@@ -657,572 +657,572 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-136250</v>
+        <v>78000</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-63209000</v>
+        <v>8816000</v>
       </c>
       <c r="E2" t="n">
-        <v>-545000</v>
+        <v>312000</v>
       </c>
       <c r="F2" t="n">
-        <v>-545000</v>
+        <v>312000</v>
       </c>
       <c r="G2" t="n">
-        <v>-75068000</v>
+        <v>3643000</v>
       </c>
       <c r="H2" t="n">
-        <v>10450000</v>
+        <v>5670000</v>
       </c>
       <c r="I2" t="n">
-        <v>58445000</v>
+        <v>44309000</v>
       </c>
       <c r="J2" t="n">
-        <v>-63754000</v>
+        <v>9128000</v>
       </c>
       <c r="K2" t="n">
-        <v>-74204000</v>
+        <v>3458000</v>
       </c>
       <c r="L2" t="n">
-        <v>843000</v>
+        <v>-209000</v>
       </c>
       <c r="M2" t="n">
-        <v>372000</v>
+        <v>474000</v>
       </c>
       <c r="N2" t="n">
-        <v>1215000</v>
+        <v>265000</v>
       </c>
       <c r="O2" t="n">
-        <v>-74659250</v>
+        <v>3409000</v>
       </c>
       <c r="P2" t="n">
-        <v>-75068000</v>
+        <v>3643000</v>
       </c>
       <c r="Q2" t="n">
-        <v>165898000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>13061000</v>
-      </c>
+        <v>96040000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>762000000</v>
+        <v>501217154</v>
       </c>
       <c r="T2" t="n">
-        <v>762000000</v>
+        <v>500986000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0985</v>
+        <v>0.0073</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0985</v>
+        <v>0.0073</v>
       </c>
       <c r="W2" t="n">
-        <v>-75068000</v>
+        <v>3643000</v>
       </c>
       <c r="X2" t="n">
-        <v>-75068000</v>
+        <v>3643000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-75068000</v>
+        <v>3643000</v>
       </c>
       <c r="AA2" t="n">
-        <v>442000</v>
+        <v>162000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-75510000</v>
+        <v>3481000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-75510000</v>
+        <v>3481000</v>
       </c>
       <c r="AD2" t="n">
-        <v>934000</v>
+        <v>-497000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-74576000</v>
+        <v>2984000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-13673000</v>
+        <v>-199000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1058000</v>
+        <v>-657000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1058000</v>
+        <v>657000</v>
       </c>
       <c r="AI2" t="n">
-        <v>843000</v>
+        <v>-209000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>372000</v>
+        <v>474000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1215000</v>
+        <v>265000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-61875000</v>
+        <v>3080000</v>
       </c>
       <c r="AM2" t="n">
-        <v>107453000</v>
+        <v>51731000</v>
       </c>
       <c r="AN2" t="n">
-        <v>32288000</v>
+        <v>23974000</v>
       </c>
       <c r="AO2" t="n">
-        <v>78803000</v>
+        <v>31891000</v>
       </c>
       <c r="AP2" t="n">
-        <v>23047000</v>
+        <v>15069000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>55756000</v>
+        <v>16822000</v>
       </c>
       <c r="AR2" t="n">
-        <v>45578000</v>
+        <v>54811000</v>
       </c>
       <c r="AS2" t="n">
-        <v>58445000</v>
+        <v>44309000</v>
       </c>
       <c r="AT2" t="n">
-        <v>104023000</v>
+        <v>99120000</v>
       </c>
       <c r="AU2" t="n">
-        <v>104023000</v>
+        <v>99120000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-2005.046503</v>
+        <v>20220</v>
       </c>
       <c r="C3" t="n">
-        <v>0.013367</v>
+        <v>0.06</v>
       </c>
       <c r="D3" t="n">
-        <v>-38246000</v>
+        <v>-8457000</v>
       </c>
       <c r="E3" t="n">
-        <v>-150000</v>
+        <v>337000</v>
       </c>
       <c r="F3" t="n">
-        <v>-150000</v>
+        <v>337000</v>
       </c>
       <c r="G3" t="n">
-        <v>-47155000</v>
+        <v>-11929000</v>
       </c>
       <c r="H3" t="n">
-        <v>9191000</v>
+        <v>6536000</v>
       </c>
       <c r="I3" t="n">
-        <v>65060000</v>
+        <v>55715000</v>
       </c>
       <c r="J3" t="n">
-        <v>-38396000</v>
+        <v>-8120000</v>
       </c>
       <c r="K3" t="n">
-        <v>-47587000</v>
+        <v>-14656000</v>
       </c>
       <c r="L3" t="n">
-        <v>2006000</v>
+        <v>526000</v>
       </c>
       <c r="M3" t="n">
-        <v>367000</v>
+        <v>357000</v>
       </c>
       <c r="N3" t="n">
-        <v>2373000</v>
+        <v>883000</v>
       </c>
       <c r="O3" t="n">
-        <v>-47007005.046503</v>
+        <v>-12245780</v>
       </c>
       <c r="P3" t="n">
-        <v>-47155000</v>
+        <v>-11929000</v>
       </c>
       <c r="Q3" t="n">
-        <v>170917000</v>
+        <v>126695000</v>
       </c>
       <c r="R3" t="n">
-        <v>7178000</v>
+        <v>987000</v>
       </c>
       <c r="S3" t="n">
-        <v>762000000</v>
+        <v>643467123</v>
       </c>
       <c r="T3" t="n">
-        <v>762000000</v>
+        <v>643467123</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0185</v>
       </c>
       <c r="W3" t="n">
-        <v>-47155000</v>
+        <v>-11929000</v>
       </c>
       <c r="X3" t="n">
-        <v>-47155000</v>
+        <v>-11929000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-47155000</v>
+        <v>-11929000</v>
       </c>
       <c r="AA3" t="n">
-        <v>158000</v>
+        <v>2196000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-47313000</v>
+        <v>-14125000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-47313000</v>
+        <v>-14125000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-641000</v>
+        <v>-888000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-47954000</v>
+        <v>-15013000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-87000</v>
+        <v>-16000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-572000</v>
+        <v>-243000</v>
       </c>
       <c r="AH3" t="n">
-        <v>572000</v>
+        <v>243000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2006000</v>
+        <v>526000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>367000</v>
+        <v>357000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2373000</v>
+        <v>883000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-50712000</v>
+        <v>-22928000</v>
       </c>
       <c r="AM3" t="n">
-        <v>105857000</v>
+        <v>70980000</v>
       </c>
       <c r="AN3" t="n">
-        <v>38922000</v>
+        <v>36592000</v>
       </c>
       <c r="AO3" t="n">
-        <v>72477000</v>
+        <v>38534000</v>
       </c>
       <c r="AP3" t="n">
-        <v>29173000</v>
+        <v>14224000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>43304000</v>
+        <v>24310000</v>
       </c>
       <c r="AR3" t="n">
-        <v>55145000</v>
+        <v>48052000</v>
       </c>
       <c r="AS3" t="n">
-        <v>65060000</v>
+        <v>55715000</v>
       </c>
       <c r="AT3" t="n">
-        <v>120205000</v>
+        <v>103767000</v>
       </c>
       <c r="AU3" t="n">
-        <v>120205000</v>
+        <v>103767000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>20220</v>
+        <v>-2005.046503</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06</v>
+        <v>0.013367</v>
       </c>
       <c r="D4" t="n">
-        <v>-8457000</v>
+        <v>-38246000</v>
       </c>
       <c r="E4" t="n">
-        <v>337000</v>
+        <v>-150000</v>
       </c>
       <c r="F4" t="n">
-        <v>337000</v>
+        <v>-150000</v>
       </c>
       <c r="G4" t="n">
-        <v>-11929000</v>
+        <v>-47155000</v>
       </c>
       <c r="H4" t="n">
-        <v>6536000</v>
+        <v>9191000</v>
       </c>
       <c r="I4" t="n">
-        <v>55715000</v>
+        <v>65060000</v>
       </c>
       <c r="J4" t="n">
-        <v>-8120000</v>
+        <v>-38396000</v>
       </c>
       <c r="K4" t="n">
-        <v>-14656000</v>
+        <v>-47587000</v>
       </c>
       <c r="L4" t="n">
-        <v>526000</v>
+        <v>2006000</v>
       </c>
       <c r="M4" t="n">
-        <v>357000</v>
+        <v>367000</v>
       </c>
       <c r="N4" t="n">
-        <v>883000</v>
+        <v>2373000</v>
       </c>
       <c r="O4" t="n">
-        <v>-12245780</v>
+        <v>-47007005.046503</v>
       </c>
       <c r="P4" t="n">
-        <v>-11929000</v>
+        <v>-47155000</v>
       </c>
       <c r="Q4" t="n">
-        <v>126695000</v>
+        <v>170917000</v>
       </c>
       <c r="R4" t="n">
-        <v>987000</v>
+        <v>7178000</v>
       </c>
       <c r="S4" t="n">
-        <v>643467123</v>
+        <v>762000000</v>
       </c>
       <c r="T4" t="n">
-        <v>643467123</v>
+        <v>762000000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0185</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0185</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>-11929000</v>
+        <v>-47155000</v>
       </c>
       <c r="X4" t="n">
-        <v>-11929000</v>
+        <v>-47155000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-11929000</v>
+        <v>-47155000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2196000</v>
+        <v>158000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-14125000</v>
+        <v>-47313000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-14125000</v>
+        <v>-47313000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-888000</v>
+        <v>-641000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-15013000</v>
+        <v>-47954000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-16000</v>
+        <v>-87000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-243000</v>
+        <v>-572000</v>
       </c>
       <c r="AH4" t="n">
-        <v>243000</v>
+        <v>572000</v>
       </c>
       <c r="AI4" t="n">
-        <v>526000</v>
+        <v>2006000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>357000</v>
+        <v>367000</v>
       </c>
       <c r="AK4" t="n">
-        <v>883000</v>
+        <v>2373000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-22928000</v>
+        <v>-50712000</v>
       </c>
       <c r="AM4" t="n">
-        <v>70980000</v>
+        <v>105857000</v>
       </c>
       <c r="AN4" t="n">
-        <v>36592000</v>
+        <v>38922000</v>
       </c>
       <c r="AO4" t="n">
-        <v>38534000</v>
+        <v>72477000</v>
       </c>
       <c r="AP4" t="n">
-        <v>14224000</v>
+        <v>29173000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24310000</v>
+        <v>43304000</v>
       </c>
       <c r="AR4" t="n">
-        <v>48052000</v>
+        <v>55145000</v>
       </c>
       <c r="AS4" t="n">
-        <v>55715000</v>
+        <v>65060000</v>
       </c>
       <c r="AT4" t="n">
-        <v>103767000</v>
+        <v>120205000</v>
       </c>
       <c r="AU4" t="n">
-        <v>103767000</v>
+        <v>120205000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>78000</v>
+        <v>-136250</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>8816000</v>
+        <v>-63209000</v>
       </c>
       <c r="E5" t="n">
-        <v>312000</v>
+        <v>-545000</v>
       </c>
       <c r="F5" t="n">
-        <v>312000</v>
+        <v>-545000</v>
       </c>
       <c r="G5" t="n">
-        <v>3643000</v>
+        <v>-75068000</v>
       </c>
       <c r="H5" t="n">
-        <v>5670000</v>
+        <v>10450000</v>
       </c>
       <c r="I5" t="n">
-        <v>44309000</v>
+        <v>58445000</v>
       </c>
       <c r="J5" t="n">
-        <v>9128000</v>
+        <v>-63754000</v>
       </c>
       <c r="K5" t="n">
-        <v>3458000</v>
+        <v>-74204000</v>
       </c>
       <c r="L5" t="n">
-        <v>-209000</v>
+        <v>843000</v>
       </c>
       <c r="M5" t="n">
-        <v>474000</v>
+        <v>372000</v>
       </c>
       <c r="N5" t="n">
-        <v>265000</v>
+        <v>1215000</v>
       </c>
       <c r="O5" t="n">
-        <v>3409000</v>
+        <v>-74659250</v>
       </c>
       <c r="P5" t="n">
-        <v>3643000</v>
+        <v>-75068000</v>
       </c>
       <c r="Q5" t="n">
-        <v>96040000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>165898000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>13061000</v>
+      </c>
       <c r="S5" t="n">
-        <v>501217154</v>
+        <v>762000000</v>
       </c>
       <c r="T5" t="n">
-        <v>500986000</v>
+        <v>762000000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0073</v>
+        <v>-0.0985</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0073</v>
+        <v>-0.0985</v>
       </c>
       <c r="W5" t="n">
-        <v>3643000</v>
+        <v>-75068000</v>
       </c>
       <c r="X5" t="n">
-        <v>3643000</v>
+        <v>-75068000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3643000</v>
+        <v>-75068000</v>
       </c>
       <c r="AA5" t="n">
-        <v>162000</v>
+        <v>442000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3481000</v>
+        <v>-75510000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3481000</v>
+        <v>-75510000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-497000</v>
+        <v>934000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2984000</v>
+        <v>-74576000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-199000</v>
+        <v>-13673000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-657000</v>
+        <v>-1058000</v>
       </c>
       <c r="AH5" t="n">
-        <v>657000</v>
+        <v>1058000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-209000</v>
+        <v>843000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>474000</v>
+        <v>372000</v>
       </c>
       <c r="AK5" t="n">
-        <v>265000</v>
+        <v>1215000</v>
       </c>
       <c r="AL5" t="n">
-        <v>3080000</v>
+        <v>-61875000</v>
       </c>
       <c r="AM5" t="n">
-        <v>51731000</v>
+        <v>107453000</v>
       </c>
       <c r="AN5" t="n">
-        <v>23974000</v>
+        <v>32288000</v>
       </c>
       <c r="AO5" t="n">
-        <v>31891000</v>
+        <v>78803000</v>
       </c>
       <c r="AP5" t="n">
-        <v>15069000</v>
+        <v>23047000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16822000</v>
+        <v>55756000</v>
       </c>
       <c r="AR5" t="n">
-        <v>54811000</v>
+        <v>45578000</v>
       </c>
       <c r="AS5" t="n">
-        <v>44309000</v>
+        <v>58445000</v>
       </c>
       <c r="AT5" t="n">
-        <v>99120000</v>
+        <v>104023000</v>
       </c>
       <c r="AU5" t="n">
-        <v>99120000</v>
+        <v>104023000</v>
       </c>
     </row>
   </sheetData>
@@ -1543,74 +1543,186 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>589530864</v>
+      </c>
+      <c r="C2" t="n">
+        <v>589530864</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11790000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>167232000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>191858000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>165550000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>167232000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1790000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>181858000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>181858000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>183655000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1797000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>181858000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2509000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>57661000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>76581000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4514000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4514000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>36647000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2249000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>119000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2058000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>72000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>72000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>34398000</v>
+      </c>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>11718000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1718000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>22680000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>20173000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>396000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2111000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>220302000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>20354000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>276000</v>
+      </c>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>14626000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>14626000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2416000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-4041000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6457000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1864000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3589000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1004000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>199948000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>488000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7948000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3384000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3384000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>92374000</v>
+      </c>
       <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>25593000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-496000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>26089000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>64061000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>64061000</v>
+      </c>
       <c r="BI2" t="n">
-        <v>165267000</v>
+        <v>64061000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>762000000</v>
@@ -1619,41 +1731,43 @@
         <v>762000000</v>
       </c>
       <c r="D3" t="n">
-        <v>14327000</v>
+        <v>12658000</v>
       </c>
       <c r="E3" t="n">
-        <v>160177000</v>
+        <v>279605000</v>
       </c>
       <c r="F3" t="n">
-        <v>174552000</v>
+        <v>299774000</v>
       </c>
       <c r="G3" t="n">
-        <v>150991000</v>
+        <v>275204000</v>
       </c>
       <c r="H3" t="n">
-        <v>160177000</v>
+        <v>279605000</v>
       </c>
       <c r="I3" t="n">
-        <v>4327000</v>
+        <v>2658000</v>
       </c>
       <c r="J3" t="n">
-        <v>164552000</v>
+        <v>289774000</v>
       </c>
       <c r="K3" t="n">
-        <v>164552000</v>
+        <v>289774000</v>
       </c>
       <c r="L3" t="n">
-        <v>164552000</v>
+        <v>289375000</v>
       </c>
       <c r="M3" t="n">
+        <v>-399000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>289774000</v>
+      </c>
+      <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>164552000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-77011000</v>
+        <v>45732000</v>
       </c>
       <c r="Q3" t="n">
         <v>192753000</v>
@@ -1665,120 +1779,130 @@
         <v>6686000</v>
       </c>
       <c r="T3" t="n">
-        <v>44256000</v>
+        <v>39997000</v>
       </c>
       <c r="U3" t="n">
-        <v>3137000</v>
+        <v>1878000</v>
       </c>
       <c r="V3" t="n">
-        <v>104000</v>
+        <v>30000</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>689000</v>
       </c>
       <c r="X3" t="n">
-        <v>3033000</v>
+        <v>1159000</v>
       </c>
       <c r="Y3" t="n">
-        <v>3033000</v>
+        <v>1159000</v>
       </c>
       <c r="Z3" t="n">
-        <v>41119000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>38119000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-30000</v>
+      </c>
       <c r="AB3" t="n">
-        <v>11294000</v>
+        <v>11499000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1294000</v>
+        <v>1499000</v>
       </c>
       <c r="AD3" t="n">
         <v>10000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>28882000</v>
+        <v>26513000</v>
       </c>
       <c r="AF3" t="n">
-        <v>9100000</v>
+        <v>11103000</v>
       </c>
       <c r="AG3" t="n">
-        <v>6648000</v>
+        <v>12723000</v>
       </c>
       <c r="AH3" t="n">
-        <v>13134000</v>
+        <v>2687000</v>
       </c>
       <c r="AI3" t="n">
-        <v>208808000</v>
+        <v>329372000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>16698000</v>
+        <v>16049000</v>
       </c>
       <c r="AK3" t="n">
-        <v>527000</v>
+        <v>45000</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>4375000</v>
+        <v>10169000</v>
       </c>
       <c r="AN3" t="n">
-        <v>4375000</v>
+        <v>10169000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8304000</v>
+        <v>3708000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-6798000</v>
+        <v>-4470000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15102000</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>8178000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2919000</v>
+      </c>
       <c r="AS3" t="n">
-        <v>8582000</v>
+        <v>4255000</v>
       </c>
       <c r="AT3" t="n">
-        <v>6520000</v>
+        <v>1004000</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>192110000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>313323000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>75000</v>
+      </c>
       <c r="AX3" t="n">
-        <v>96000</v>
+        <v>4333000</v>
       </c>
       <c r="AY3" t="n">
-        <v>11044000</v>
+        <v>6323000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10747000</v>
+        <v>4531000</v>
       </c>
       <c r="BA3" t="n">
-        <v>10747000</v>
+        <v>4531000</v>
       </c>
       <c r="BB3" t="n">
-        <v>77918000</v>
+        <v>98912000</v>
       </c>
       <c r="BC3" t="n">
         <v>1491000</v>
       </c>
       <c r="BD3" t="n">
-        <v>13493000</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+        <v>26292000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-524000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>26386000</v>
+      </c>
       <c r="BG3" t="n">
-        <v>77321000</v>
+        <v>171366000</v>
       </c>
       <c r="BH3" t="n">
-        <v>77321000</v>
+        <v>171366000</v>
       </c>
       <c r="BI3" t="n">
-        <v>77321000</v>
+        <v>171366000</v>
       </c>
     </row>
     <row r="4">
@@ -1958,7 +2082,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>762000000</v>
@@ -1967,43 +2091,41 @@
         <v>762000000</v>
       </c>
       <c r="D5" t="n">
-        <v>12658000</v>
+        <v>14327000</v>
       </c>
       <c r="E5" t="n">
-        <v>279605000</v>
+        <v>160177000</v>
       </c>
       <c r="F5" t="n">
-        <v>299774000</v>
+        <v>174552000</v>
       </c>
       <c r="G5" t="n">
-        <v>275204000</v>
+        <v>150991000</v>
       </c>
       <c r="H5" t="n">
-        <v>279605000</v>
+        <v>160177000</v>
       </c>
       <c r="I5" t="n">
-        <v>2658000</v>
+        <v>4327000</v>
       </c>
       <c r="J5" t="n">
-        <v>289774000</v>
+        <v>164552000</v>
       </c>
       <c r="K5" t="n">
-        <v>289774000</v>
+        <v>164552000</v>
       </c>
       <c r="L5" t="n">
-        <v>289375000</v>
+        <v>164552000</v>
       </c>
       <c r="M5" t="n">
-        <v>-399000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>289774000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
+        <v>164552000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>45732000</v>
+        <v>-77011000</v>
       </c>
       <c r="Q5" t="n">
         <v>192753000</v>
@@ -2015,309 +2137,187 @@
         <v>6686000</v>
       </c>
       <c r="T5" t="n">
-        <v>39997000</v>
+        <v>44256000</v>
       </c>
       <c r="U5" t="n">
-        <v>1878000</v>
+        <v>3137000</v>
       </c>
       <c r="V5" t="n">
-        <v>30000</v>
+        <v>104000</v>
       </c>
       <c r="W5" t="n">
-        <v>689000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1159000</v>
+        <v>3033000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1159000</v>
+        <v>3033000</v>
       </c>
       <c r="Z5" t="n">
-        <v>38119000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-30000</v>
-      </c>
+        <v>41119000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>11499000</v>
+        <v>11294000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1499000</v>
+        <v>1294000</v>
       </c>
       <c r="AD5" t="n">
         <v>10000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>26513000</v>
+        <v>28882000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11103000</v>
+        <v>9100000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12723000</v>
+        <v>6648000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2687000</v>
+        <v>13134000</v>
       </c>
       <c r="AI5" t="n">
-        <v>329372000</v>
+        <v>208808000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16049000</v>
+        <v>16698000</v>
       </c>
       <c r="AK5" t="n">
-        <v>45000</v>
+        <v>527000</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>10169000</v>
+        <v>4375000</v>
       </c>
       <c r="AN5" t="n">
-        <v>10169000</v>
+        <v>4375000</v>
       </c>
       <c r="AO5" t="n">
-        <v>3708000</v>
+        <v>8304000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-4470000</v>
+        <v>-6798000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8178000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2919000</v>
-      </c>
+        <v>15102000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>4255000</v>
+        <v>8582000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1004000</v>
+        <v>6520000</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>313323000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>75000</v>
-      </c>
+        <v>192110000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>4333000</v>
+        <v>96000</v>
       </c>
       <c r="AY5" t="n">
-        <v>6323000</v>
+        <v>11044000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4531000</v>
+        <v>10747000</v>
       </c>
       <c r="BA5" t="n">
-        <v>4531000</v>
+        <v>10747000</v>
       </c>
       <c r="BB5" t="n">
-        <v>98912000</v>
+        <v>77918000</v>
       </c>
       <c r="BC5" t="n">
         <v>1491000</v>
       </c>
       <c r="BD5" t="n">
-        <v>26292000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-524000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>26386000</v>
-      </c>
+        <v>13493000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>171366000</v>
+        <v>77321000</v>
       </c>
       <c r="BH5" t="n">
-        <v>171366000</v>
+        <v>77321000</v>
       </c>
       <c r="BI5" t="n">
-        <v>171366000</v>
+        <v>77321000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>589530864</v>
-      </c>
-      <c r="C6" t="n">
-        <v>589530864</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11790000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>167232000</v>
-      </c>
-      <c r="F6" t="n">
-        <v>191858000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>165550000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>167232000</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1790000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>181858000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>181858000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>183655000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1797000</v>
-      </c>
-      <c r="N6" t="n">
-        <v>181858000</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2509000</v>
-      </c>
-      <c r="P6" t="n">
-        <v>57661000</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>76581000</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4514000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4514000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>36647000</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2249000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>119000</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2058000</v>
-      </c>
-      <c r="X6" t="n">
-        <v>72000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>72000</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>34398000</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="n">
-        <v>11718000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1718000</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>22680000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>20173000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>396000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2111000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>220302000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>20354000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>276000</v>
-      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
-        <v>14626000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>14626000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>2416000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-4041000</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>6457000</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1864000</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3589000</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1004000</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>199948000</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>488000</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6100000</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7948000</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>3384000</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3384000</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>92374000</v>
-      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>25593000</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-496000</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>26089000</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>64061000</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>64061000</v>
-      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="n">
-        <v>64061000</v>
+        <v>165267000</v>
       </c>
     </row>
   </sheetData>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-42453000</v>
+        <v>-17530000</v>
       </c>
       <c r="C2" t="n">
         <v>-10000000</v>
@@ -2589,33 +2589,39 @@
       <c r="D2" t="n">
         <v>10000000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>-5018000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-4175000</v>
+        <v>-5798000</v>
       </c>
       <c r="G2" t="n">
-        <v>77321000</v>
+        <v>64061000</v>
       </c>
       <c r="H2" t="n">
-        <v>122620000</v>
+        <v>85912000</v>
       </c>
       <c r="I2" t="n">
-        <v>674000</v>
+        <v>-154000</v>
       </c>
       <c r="J2" t="n">
-        <v>-45973000</v>
+        <v>-21697000</v>
       </c>
       <c r="K2" t="n">
-        <v>-4188000</v>
+        <v>-5136000</v>
       </c>
       <c r="L2" t="n">
-        <v>301000</v>
+        <v>2224000</v>
       </c>
       <c r="M2" t="n">
-        <v>-605000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-474000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-5018000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-5018000</v>
+      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
@@ -2628,95 +2634,99 @@
       <c r="S2" t="n">
         <v>10000000</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>10000000</v>
+      </c>
       <c r="W2" t="n">
-        <v>-3507000</v>
+        <v>-4829000</v>
       </c>
       <c r="X2" t="n">
-        <v>513000</v>
+        <v>969000</v>
       </c>
       <c r="Y2" t="n">
-        <v>247013000</v>
+        <v>441129000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-246500000</v>
+        <v>-440160000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1230000</v>
+        <v>-5350000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1230000</v>
+        <v>-5350000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2790000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>155000</v>
-      </c>
+        <v>-448000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>-2945000</v>
+        <v>-448000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-38278000</v>
+        <v>-11732000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-467000</v>
+        <v>-416000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1129000</v>
+        <v>209000</v>
       </c>
       <c r="AI2" t="n">
-        <v>12505000</v>
+        <v>-23747000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-297000</v>
+        <v>-600000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3408000</v>
+        <v>-2742000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1658000</v>
+        <v>-4681000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-4758000</v>
+        <v>-2031000</v>
       </c>
       <c r="AN2" t="n">
-        <v>22626000</v>
+        <v>-13693000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-843000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>209000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3517000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>10450000</v>
+        <v>5670000</v>
       </c>
       <c r="AR2" t="n">
-        <v>4743000</v>
+        <v>3524000</v>
       </c>
       <c r="AS2" t="n">
-        <v>5707000</v>
+        <v>2146000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-513000</v>
+        <v>-969000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-674000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6000</v>
-      </c>
+        <v>154000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>-74576000</v>
+        <v>2984000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-45611000</v>
+        <v>-17406000</v>
       </c>
       <c r="C3" t="n">
         <v>-10000000</v>
@@ -2725,37 +2735,37 @@
         <v>10000000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>119450000</v>
       </c>
       <c r="F3" t="n">
-        <v>-18840000</v>
+        <v>-666000</v>
       </c>
       <c r="G3" t="n">
-        <v>122620000</v>
+        <v>171366000</v>
       </c>
       <c r="H3" t="n">
-        <v>171366000</v>
+        <v>64061000</v>
       </c>
       <c r="I3" t="n">
-        <v>989000</v>
+        <v>7068000</v>
       </c>
       <c r="J3" t="n">
-        <v>-49735000</v>
+        <v>100237000</v>
       </c>
       <c r="K3" t="n">
-        <v>-4546000</v>
+        <v>117063000</v>
       </c>
       <c r="L3" t="n">
-        <v>-496000</v>
+        <v>1255000</v>
       </c>
       <c r="M3" t="n">
-        <v>-367000</v>
+        <v>-357000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>119450000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>119450000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -2773,93 +2783,89 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-18418000</v>
+        <v>-86000</v>
       </c>
       <c r="X3" t="n">
-        <v>422000</v>
+        <v>580000</v>
       </c>
       <c r="Y3" t="n">
-        <v>200422000</v>
+        <v>256580000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-200000000</v>
+        <v>-256000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-15900000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-15900000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2940000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
+        <v>-666000</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-2940000</v>
+        <v>-666000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-26771000</v>
+        <v>-16740000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-516000</v>
+        <v>-877000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2296000</v>
+        <v>821000</v>
       </c>
       <c r="AI3" t="n">
-        <v>13057000</v>
+        <v>-2119000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-637000</v>
+        <v>338000</v>
       </c>
       <c r="AK3" t="n">
-        <v>6687000</v>
+        <v>4247000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-5999000</v>
+        <v>822000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1457000</v>
+        <v>-1147000</v>
       </c>
       <c r="AN3" t="n">
-        <v>14463000</v>
+        <v>-6379000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2006000</v>
+        <v>-526000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1843000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9191000</v>
+        <v>6536000</v>
       </c>
       <c r="AR3" t="n">
-        <v>4534000</v>
+        <v>4457000</v>
       </c>
       <c r="AS3" t="n">
-        <v>4657000</v>
+        <v>2079000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-422000</v>
+        <v>-580000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-989000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
+        <v>-7068000</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>-47954000</v>
+        <v>-15013000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-17406000</v>
+        <v>-45611000</v>
       </c>
       <c r="C4" t="n">
         <v>-10000000</v>
@@ -2868,37 +2874,37 @@
         <v>10000000</v>
       </c>
       <c r="E4" t="n">
-        <v>119450000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-666000</v>
+        <v>-18840000</v>
       </c>
       <c r="G4" t="n">
+        <v>122620000</v>
+      </c>
+      <c r="H4" t="n">
         <v>171366000</v>
       </c>
-      <c r="H4" t="n">
-        <v>64061000</v>
-      </c>
       <c r="I4" t="n">
-        <v>7068000</v>
+        <v>989000</v>
       </c>
       <c r="J4" t="n">
-        <v>100237000</v>
+        <v>-49735000</v>
       </c>
       <c r="K4" t="n">
-        <v>117063000</v>
+        <v>-4546000</v>
       </c>
       <c r="L4" t="n">
-        <v>1255000</v>
+        <v>-496000</v>
       </c>
       <c r="M4" t="n">
-        <v>-357000</v>
+        <v>-367000</v>
       </c>
       <c r="N4" t="n">
-        <v>119450000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>119450000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -2916,89 +2922,93 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-86000</v>
+        <v>-18418000</v>
       </c>
       <c r="X4" t="n">
-        <v>580000</v>
+        <v>422000</v>
       </c>
       <c r="Y4" t="n">
-        <v>256580000</v>
+        <v>200422000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-256000000</v>
+        <v>-200000000</v>
       </c>
       <c r="AA4" t="n">
+        <v>-15900000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-15900000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2940000</v>
+      </c>
+      <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
+        <v>-2940000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-26771000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-516000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2296000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>13057000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-637000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>6687000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-5999000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-1457000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>14463000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-2006000</v>
+      </c>
+      <c r="AP4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" t="n">
-        <v>-666000</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="n">
-        <v>-666000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-16740000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-877000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>821000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-2119000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>338000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>4247000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>822000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1147000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-6379000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-526000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1843000</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>6536000</v>
+        <v>9191000</v>
       </c>
       <c r="AR4" t="n">
-        <v>4457000</v>
+        <v>4534000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2079000</v>
+        <v>4657000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-580000</v>
+        <v>-422000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-7068000</v>
-      </c>
-      <c r="AV4" t="inlineStr"/>
+        <v>-989000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
       <c r="AW4" t="n">
-        <v>-15013000</v>
+        <v>-47954000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-17530000</v>
+        <v>-42453000</v>
       </c>
       <c r="C5" t="n">
         <v>-10000000</v>
@@ -3006,39 +3016,33 @@
       <c r="D5" t="n">
         <v>10000000</v>
       </c>
-      <c r="E5" t="n">
-        <v>-5018000</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-5798000</v>
+        <v>-4175000</v>
       </c>
       <c r="G5" t="n">
-        <v>64061000</v>
+        <v>77321000</v>
       </c>
       <c r="H5" t="n">
-        <v>85912000</v>
+        <v>122620000</v>
       </c>
       <c r="I5" t="n">
-        <v>-154000</v>
+        <v>674000</v>
       </c>
       <c r="J5" t="n">
-        <v>-21697000</v>
+        <v>-45973000</v>
       </c>
       <c r="K5" t="n">
-        <v>-5136000</v>
+        <v>-4188000</v>
       </c>
       <c r="L5" t="n">
-        <v>2224000</v>
+        <v>301000</v>
       </c>
       <c r="M5" t="n">
-        <v>-474000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-5018000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-5018000</v>
-      </c>
+        <v>-605000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
@@ -3051,91 +3055,87 @@
       <c r="S5" t="n">
         <v>10000000</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>10000000</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>-4829000</v>
+        <v>-3507000</v>
       </c>
       <c r="X5" t="n">
-        <v>969000</v>
+        <v>513000</v>
       </c>
       <c r="Y5" t="n">
-        <v>441129000</v>
+        <v>247013000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-440160000</v>
+        <v>-246500000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-5350000</v>
+        <v>-1230000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-5350000</v>
+        <v>-1230000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-448000</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>-2790000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>155000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-448000</v>
+        <v>-2945000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-11732000</v>
+        <v>-38278000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-416000</v>
+        <v>-467000</v>
       </c>
       <c r="AH5" t="n">
-        <v>209000</v>
+        <v>1129000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-23747000</v>
+        <v>12505000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-600000</v>
+        <v>-297000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-2742000</v>
+        <v>-3408000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-4681000</v>
+        <v>-1658000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-2031000</v>
+        <v>-4758000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-13693000</v>
+        <v>22626000</v>
       </c>
       <c r="AO5" t="n">
-        <v>209000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3517000</v>
-      </c>
+        <v>-843000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>5670000</v>
+        <v>10450000</v>
       </c>
       <c r="AR5" t="n">
-        <v>3524000</v>
+        <v>4743000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2146000</v>
+        <v>5707000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-969000</v>
+        <v>-513000</v>
       </c>
       <c r="AU5" t="n">
-        <v>154000</v>
-      </c>
-      <c r="AV5" t="inlineStr"/>
+        <v>-674000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6000</v>
+      </c>
       <c r="AW5" t="n">
-        <v>2984000</v>
+        <v>-74576000</v>
       </c>
     </row>
   </sheetData>
@@ -3655,197 +3655,197 @@
       </c>
       <c r="CW1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Zhimin  Shi', 'age': 45, 'title': 'CEO &amp; Executive Chairman', 'yearBorn': 1980, 'fiscalYear': 2025, 'totalPay': 845662, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Chun Yu  Sie', 'age': 53, 'title': 'Financial Controller', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yong  Yue', 'age': 53, 'title': 'Chief Technology Officer of Vixtel Technologies Limited', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 430940, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tak Kwan  Sie', 'age': 49, 'title': 'Financial Director of Vixtel Technologies Limited', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 540992, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zewei  Liu', 'age': 43, 'title': 'Head of the Product Marketing Department of Vixtel Technologies Limited', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ngai Chi  Chan C.F.A., FCCA, FCPA', 'age': 53, 'title': 'Company Secretary', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Zhimin  Shi', 'age': 45, 'title': 'CEO &amp; Executive Chairman', 'yearBorn': 1980, 'fiscalYear': 2025, 'totalPay': 844988, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Chun Yu  Sie', 'age': 53, 'title': 'Financial Controller', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yong  Yue', 'age': 53, 'title': 'Chief Technology Officer of Vixtel Technologies Limited', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 430597, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tak Kwan  Sie', 'age': 49, 'title': 'Financial Director of Vixtel Technologies Limited', 'yearBorn': 1976, 'fiscalYear': 2025, 'totalPay': 540561, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zewei  Liu', 'age': 43, 'title': 'Head of the Product Marketing Department of Vixtel Technologies Limited', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ngai Chi  Chan C.F.A., FCCA, FCPA', 'age': 53, 'title': 'Company Secretary', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3938,28 +3938,28 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="U2" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>3.63</v>
+        <v>3.16</v>
       </c>
       <c r="W2" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.63</v>
+        <v>3.16</v>
       </c>
       <c r="AA2" t="n">
         <v>1558396800</v>
@@ -3968,28 +3968,28 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.267</v>
+        <v>-0.238</v>
       </c>
       <c r="AD2" t="n">
-        <v>45000</v>
+        <v>125000</v>
       </c>
       <c r="AE2" t="n">
-        <v>45000</v>
+        <v>125000</v>
       </c>
       <c r="AF2" t="n">
-        <v>89833</v>
+        <v>99067</v>
       </c>
       <c r="AG2" t="n">
-        <v>40000</v>
+        <v>82000</v>
       </c>
       <c r="AH2" t="n">
-        <v>40000</v>
+        <v>82000</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.43</v>
+        <v>2.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.79</v>
+        <v>3.15</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -3998,13 +3998,13 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2800000000</v>
+        <v>2520000000</v>
       </c>
       <c r="AN2" t="n">
-        <v>2904000000</v>
+        <v>2400000000</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="AP2" t="n">
         <v>5.2</v>
@@ -4016,13 +4016,13 @@
         <v>0.25851</v>
       </c>
       <c r="AS2" t="n">
-        <v>26.71399</v>
+        <v>24.04259</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5878</v>
+        <v>3.4864</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.03995</v>
+        <v>4.03155</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2762729984</v>
+        <v>2378729984</v>
       </c>
       <c r="BA2" t="n">
         <v>-0.55972</v>
@@ -4060,10 +4060,10 @@
         <v>800000000</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.33701926</v>
+        <v>0.33684042</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.385163</v>
+        <v>9.351609</v>
       </c>
       <c r="BI2" t="n">
         <v>1767139200</v>
@@ -4081,16 +4081,16 @@
         <v>-0.09</v>
       </c>
       <c r="BN2" t="n">
-        <v>26.358</v>
+        <v>22.695</v>
       </c>
       <c r="BO2" t="n">
-        <v>-47.171</v>
+        <v>-40.614</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.069230795</v>
+        <v>-0.122807026</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="n">
         <v>0.01034</v>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -4204,149 +4204,149 @@
         </is>
       </c>
       <c r="CW2" t="n">
-        <v>3.5</v>
+        <v>0.1500001</v>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>IB DIGITAL TECH</t>
+          <t>3.0 - 3.16</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>International Business Digital Technology Limited</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>99067</v>
       </c>
       <c r="DA2" t="n">
-        <v>1780300508</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
+        <v>0.20000005</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.067796625</v>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>finmb_410446489</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
+          <t>2.95 - 5.2</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>-2.0499997</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.39423072</v>
       </c>
       <c r="DF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DH2" t="b">
-        <v>0</v>
+        <v>-12.280703</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1742907514</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1742907514</v>
       </c>
       <c r="DI2" t="b">
         <v>0</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1481851800000</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>5.0000033</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="DO2" t="n">
         <v>-0.09</v>
       </c>
-      <c r="DK2" t="n">
-        <v>-0.087800026</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.024471829</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.5399499</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.13365263</v>
-      </c>
-      <c r="DO2" t="n">
+      <c r="DP2" t="n">
+        <v>-0.3363998</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.09648916</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.88154984</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.21866275</v>
+      </c>
+      <c r="DT2" t="n">
         <v>15</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DU2" t="n">
         <v>15</v>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>Vixtel Technologies Holdings Limited</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>1782114578</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>finmb_410446489</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EF2" t="b">
         <v>0</v>
       </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1481851800000</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.13000011</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>3.31 - 3.63</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>89833</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.4100001</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.13268611</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>3.09 - 5.2</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>-1.6999998</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.32692304</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-6.9230795</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1742907514</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1742907514</v>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>IB DIGITAL TECH</t>
+        </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>-3.5812702</v>
+          <t>International Business Digital Technology Limited</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
